--- a/clustvartools/datasets/data/burger.xlsx
+++ b/clustvartools/datasets/data/burger.xlsx
@@ -4,6 +4,8 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Feuil1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Feuil2" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Feuil3" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="32">
   <si>
     <t>ITEM</t>
   </si>
@@ -37,6 +39,9 @@
     <t>Sodium</t>
   </si>
   <si>
+    <t>Serving_size</t>
+  </si>
+  <si>
     <t>Carbs</t>
   </si>
   <si>
@@ -46,13 +51,10 @@
     <t>Sugar</t>
   </si>
   <si>
-    <t>Serving_size</t>
+    <t>BK__Double_Stacker</t>
   </si>
   <si>
     <t>Meat</t>
-  </si>
-  <si>
-    <t>BK__Double_Stacker</t>
   </si>
   <si>
     <t>yes</t>
@@ -186,6 +188,14 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -395,6 +405,2834 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="32.25"/>
+    <col customWidth="1" min="2" max="11" width="7.0"/>
+    <col customWidth="1" min="12" max="24" width="9.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4">
+        <v>3.237</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1.8497</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.1734</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.2081</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.0867</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.6358</v>
+      </c>
+      <c r="H2" s="4">
+        <v>6.0116</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0.1676</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0.0058</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0.0405</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2.9412</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.5294</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1647</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.1706</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.0294</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.3235</v>
+      </c>
+      <c r="H3" s="4">
+        <v>9.5882</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1882</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.0176</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0.0059</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2.5949</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.2658</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1519</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.1392</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.0633</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.538</v>
+      </c>
+      <c r="H4" s="4">
+        <v>4.6835</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.1772</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.0063</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="4">
+        <v>3.0986</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1.7606</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.0845</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.1972</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.0317</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.2465</v>
+      </c>
+      <c r="H5" s="4">
+        <v>4.2958</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2465</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.007</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0.0282</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1.6763</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.4046</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.0347</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.0462</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.0405</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.1156</v>
+      </c>
+      <c r="H6" s="4">
+        <v>1.3295</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3064</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.0058</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0.2601</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="4">
+        <v>3.6719</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1.5625</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.0469</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.1719</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.0781</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0.0391</v>
+      </c>
+      <c r="H7" s="4">
+        <v>4.0625</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.4844</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.0078</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0.2266</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2.6316</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1.345</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.152</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.152</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.0702</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.5556</v>
+      </c>
+      <c r="H8" s="4">
+        <v>5.614</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1696</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.0058</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0.0351</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="4">
+        <v>2.4658</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1.0959</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.1507</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.1233</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.0548</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.4795</v>
+      </c>
+      <c r="H9" s="4">
+        <v>3.5616</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.1918</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.0068</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0.0411</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2.8177</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1.4917</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.1713</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.1657</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.0773</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.5801</v>
+      </c>
+      <c r="H10" s="4">
+        <v>6.3536</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1602</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.0055</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0.0387</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0.4321</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.216</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.0247</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.0247</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0.0154</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0.0617</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.6173</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.0432</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.0185</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0.0123</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1.4159</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.3982</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.0619</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0.0442</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0.0133</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0.0885</v>
+      </c>
+      <c r="H12" s="4">
+        <v>3.0088</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1947</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.0088</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0.0442</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="4">
+        <v>3.6283</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1.8584</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0.0442</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0.2035</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0.0398</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0.7522</v>
+      </c>
+      <c r="H13" s="4">
+        <v>3.5398</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.4248</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.0177</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0.3097</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2.2105</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0.7368</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0.1263</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0.0842</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0.0184</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0.2368</v>
+      </c>
+      <c r="H14" s="4">
+        <v>6.3684</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.2421</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.0158</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0.0211</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="4">
+        <v>2.7344</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.1328</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0.0547</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.3516</v>
+      </c>
+      <c r="H15" s="4">
+        <v>4.6875</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2891</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.0156</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0.0703</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="4">
+        <v>3.3824</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1.9853</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0.0956</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.2206</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.0368</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.2206</v>
+      </c>
+      <c r="H16" s="4">
+        <v>5.9559</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.0147</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0.0294</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="4">
+        <v>2.6316</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0.9649</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.1053</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0.1053</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0.0219</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0.1754</v>
+      </c>
+      <c r="H17" s="4">
+        <v>5.8772</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.307</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.0175</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0.0351</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1.8966</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1.1494</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0.0805</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0.1322</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0.046</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0.1724</v>
+      </c>
+      <c r="H18" s="4">
+        <v>4.3103</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.1034</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0.0287</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0.023</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
+    <row r="543"/>
+    <row r="544"/>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547"/>
+    <row r="548"/>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937"/>
+    <row r="938"/>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952"/>
+    <row r="953"/>
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
+    <row r="965"/>
+    <row r="966"/>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
+    <row r="993"/>
+    <row r="994"/>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
+  </sheetData>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="32.25"/>
+    <col customWidth="1" min="2" max="3" width="7.0"/>
+    <col customWidth="1" min="4" max="16" width="9.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4">
+        <v>173.0</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="4">
+        <v>170.0</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="4">
+        <v>158.0</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="4">
+        <v>142.0</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4">
+        <v>173.0</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="4">
+        <v>128.0</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="4">
+        <v>171.0</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="4">
+        <v>146.0</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="4">
+        <v>181.0</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="4">
+        <v>162.0</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="4">
+        <v>113.0</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="4">
+        <v>113.0</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="4">
+        <v>190.0</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="4">
+        <v>128.0</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="4">
+        <v>136.0</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="4">
+        <v>114.0</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="4">
+        <v>174.0</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
+    <row r="543"/>
+    <row r="544"/>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547"/>
+    <row r="548"/>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937"/>
+    <row r="938"/>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952"/>
+    <row r="953"/>
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
+    <row r="965"/>
+    <row r="966"/>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
+    <row r="993"/>
+    <row r="994"/>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
+  </sheetData>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="32.25"/>
     <col customWidth="1" min="2" max="13" width="7.0"/>
     <col customWidth="1" min="14" max="26" width="9.38"/>
   </cols>
@@ -425,24 +3263,24 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="M1" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4">
         <v>3.237</v>
